--- a/output/resultat.xlsx
+++ b/output/resultat.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>EAN</t>
   </si>
@@ -22,12 +22,6 @@
   </si>
   <si>
     <t>status</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>IMAGE_NOT_FOUND</t>
   </si>
 </sst>
 </file>
@@ -307,7 +301,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col min="2" max="2" width="8.65625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="5.7265625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -325,1815 +319,825 @@
       <c r="A2" s="2">
         <v>8.935341246799E12</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2">
         <v>8.935341246447E12</v>
       </c>
-      <c r="B3" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2">
         <v>8.935341246478E12</v>
       </c>
-      <c r="B4" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="2">
         <v>8.935341246485E12</v>
       </c>
-      <c r="B5" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="2">
         <v>8.935341246768E12</v>
       </c>
-      <c r="B6" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="2">
         <v>8.848116047609E12</v>
       </c>
-      <c r="B7" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="2">
         <v>8.848116047333E12</v>
       </c>
-      <c r="B8" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="2">
         <v>8.935341246508E12</v>
       </c>
-      <c r="B9" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="2">
         <v>8.848116047715E12</v>
       </c>
-      <c r="B10" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C10" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="2">
         <v>8.935341232877E12</v>
       </c>
-      <c r="B11" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C11" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="2">
         <v>8.848116026376E12</v>
       </c>
-      <c r="B12" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C12" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="2">
         <v>8.93534123301E12</v>
       </c>
-      <c r="B13" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C13" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="2">
         <v>8.935341232518E12</v>
       </c>
-      <c r="B14" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C14" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="2">
         <v>8.935341232495E12</v>
       </c>
-      <c r="B15" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C15" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="2">
         <v>8.935341232532E12</v>
       </c>
-      <c r="B16" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C16" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="2">
         <v>8.935341232556E12</v>
       </c>
-      <c r="B17" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C17" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="2">
         <v>8.84811602626E12</v>
       </c>
-      <c r="B18" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C18" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="2">
         <v>8.935341232891E12</v>
       </c>
-      <c r="B19" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C19" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="2">
         <v>8.935341233003E12</v>
       </c>
-      <c r="B20" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C20" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="2">
         <v>8.93534123299E12</v>
       </c>
-      <c r="B21" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C21" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="2">
         <v>8.935341246775E12</v>
       </c>
-      <c r="B22" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C22" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="2">
         <v>8.935341246683E12</v>
       </c>
-      <c r="B23" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C23" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="2">
         <v>8.848116047562E12</v>
       </c>
-      <c r="B24" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C24" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="2">
         <v>8.935341246553E12</v>
       </c>
-      <c r="B25" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C25" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="2">
         <v>8.935341246539E12</v>
       </c>
-      <c r="B26" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C26" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="2">
         <v>8.84811604763E12</v>
       </c>
-      <c r="B27" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C27" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="2">
         <v>8.93534124656E12</v>
       </c>
-      <c r="B28" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C28" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="2">
         <v>8.935341246591E12</v>
       </c>
-      <c r="B29" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C29" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="2">
         <v>8.848116047456E12</v>
       </c>
-      <c r="B30" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C30" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="2">
         <v>8.935341246751E12</v>
       </c>
-      <c r="B31" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C31" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="2">
         <v>8.848116047722E12</v>
       </c>
-      <c r="B32" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C32" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="2">
         <v>8.848116047654E12</v>
       </c>
-      <c r="B33" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C33" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="2">
         <v>8.935341246737E12</v>
       </c>
-      <c r="B34" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C34" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="2">
         <v>8.935341246706E12</v>
       </c>
-      <c r="B35" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C35" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="2">
         <v>8.935341246713E12</v>
       </c>
-      <c r="B36" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C36" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="2">
         <v>8.93534124672E12</v>
       </c>
-      <c r="B37" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C37" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="2">
         <v>8.935341246584E12</v>
       </c>
-      <c r="B38" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C38" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" s="2">
         <v>8.935341246577E12</v>
       </c>
-      <c r="B39" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C39" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="2">
         <v>8.935341246652E12</v>
       </c>
-      <c r="B40" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C40" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="2">
         <v>8.935341251021E12</v>
       </c>
-      <c r="B41" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C41" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="2">
         <v>8.848116047678E12</v>
       </c>
-      <c r="B42" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C42" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" s="2">
         <v>8.935341251038E12</v>
       </c>
-      <c r="B43" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C43" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="2">
         <v>8.935341246782E12</v>
       </c>
-      <c r="B44" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C44" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" s="2">
         <v>8.84811602709E12</v>
       </c>
-      <c r="B45" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C45" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" s="2">
         <v>8.848116027106E12</v>
       </c>
-      <c r="B46" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C46" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" s="2">
         <v>8.848116027205E12</v>
       </c>
-      <c r="B47" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C47" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" s="2">
         <v>8.935341234352E12</v>
       </c>
-      <c r="B48" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C48" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" s="2">
         <v>8.935341234222E12</v>
       </c>
-      <c r="B49" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C49" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" s="2">
         <v>8.935341243842E12</v>
       </c>
-      <c r="B50" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C50" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" s="2">
         <v>8.935341234017E12</v>
       </c>
-      <c r="B51" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C51" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" s="2">
         <v>8.935341234024E12</v>
       </c>
-      <c r="B52" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C52" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" s="2">
         <v>8.935341234048E12</v>
       </c>
-      <c r="B53" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C53" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" s="2">
         <v>8.935341234055E12</v>
       </c>
-      <c r="B54" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C54" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" s="2">
         <v>8.935341234079E12</v>
       </c>
-      <c r="B55" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C55" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" s="2">
         <v>8.848116027113E12</v>
       </c>
-      <c r="B56" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C56" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" s="2">
         <v>8.935341234109E12</v>
       </c>
-      <c r="B57" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C57" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" s="2">
         <v>8.93534121954E12</v>
       </c>
-      <c r="B58" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C58" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" s="2">
         <v>8.935341219502E12</v>
       </c>
-      <c r="B59" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C59" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" s="2">
         <v>8.848116027427E12</v>
       </c>
-      <c r="B60" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C60" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" s="2">
         <v>8.848116027267E12</v>
       </c>
-      <c r="B61" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C61" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" s="2">
         <v>8.935341219519E12</v>
       </c>
-      <c r="B62" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C62" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" s="2">
         <v>8.935341234369E12</v>
       </c>
-      <c r="B63" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C63" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" s="2">
         <v>8.935341234062E12</v>
       </c>
-      <c r="B64" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C64" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" s="2">
         <v>8.848116027236E12</v>
       </c>
-      <c r="B65" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C65" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" s="2">
         <v>8.935341234376E12</v>
       </c>
-      <c r="B66" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C66" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" s="2">
         <v>8.935341234116E12</v>
       </c>
-      <c r="B67" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C67" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" s="2">
         <v>8.848116027243E12</v>
       </c>
-      <c r="B68" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C68" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" s="2">
         <v>8.93534123413E12</v>
       </c>
-      <c r="B69" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C69" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" s="2">
         <v>8.848116027403E12</v>
       </c>
-      <c r="B70" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C70" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" s="2">
         <v>8.84811602767E12</v>
       </c>
-      <c r="B71" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C71" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" s="2">
         <v>8.84811602741E12</v>
       </c>
-      <c r="B72" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C72" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" s="2">
         <v>8.935341219564E12</v>
       </c>
-      <c r="B73" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C73" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" s="2">
         <v>8.935341219526E12</v>
       </c>
-      <c r="B74" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C74" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" s="2">
         <v>8.84811602738E12</v>
       </c>
-      <c r="B75" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C75" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76" s="2">
         <v>8.935341234291E12</v>
       </c>
-      <c r="B76" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C76" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" s="2">
         <v>8.935341234468E12</v>
       </c>
-      <c r="B77" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C77" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" s="2">
         <v>8.848116027373E12</v>
       </c>
-      <c r="B78" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C78" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79" s="2">
         <v>8.848116027397E12</v>
       </c>
-      <c r="B79" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C79" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" s="2">
         <v>8.848116027564E12</v>
       </c>
-      <c r="B80" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C80" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" s="2">
         <v>8.935341234512E12</v>
       </c>
-      <c r="B81" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C81" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" s="2">
         <v>8.84811602712E12</v>
       </c>
-      <c r="B82" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C82" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" s="2">
         <v>8.848116027311E12</v>
       </c>
-      <c r="B83" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C83" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" s="2">
         <v>8.848116027465E12</v>
       </c>
-      <c r="B84" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C84" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" s="2">
         <v>8.84811602725E12</v>
       </c>
-      <c r="B85" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C85" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" s="2">
         <v>8.935341243828E12</v>
       </c>
-      <c r="B86" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C86" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="87">
       <c r="A87" s="2">
         <v>8.848116027434E12</v>
       </c>
-      <c r="B87" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C87" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88" s="2">
         <v>8.848116027328E12</v>
       </c>
-      <c r="B88" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C88" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" s="2">
         <v>8.848116027458E12</v>
       </c>
-      <c r="B89" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C89" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" s="2">
         <v>8.935341234505E12</v>
       </c>
-      <c r="B90" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C90" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91" s="2">
         <v>8.935341219533E12</v>
       </c>
-      <c r="B91" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C91" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92" s="2">
         <v>8.935341234543E12</v>
       </c>
-      <c r="B92" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C92" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" s="2">
         <v>8.848116027496E12</v>
       </c>
-      <c r="B93" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C93" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" s="2">
         <v>8.848116027663E12</v>
       </c>
-      <c r="B94" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C94" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" s="2">
         <v>8.848116027526E12</v>
       </c>
-      <c r="B95" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C95" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" s="2">
         <v>8.848116027557E12</v>
       </c>
-      <c r="B96" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C96" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" s="2">
         <v>8.848116027137E12</v>
       </c>
-      <c r="B97" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C97" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="98">
       <c r="A98" s="2">
         <v>8.935341234635E12</v>
       </c>
-      <c r="B98" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C98" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99" s="2">
         <v>8.935341234642E12</v>
       </c>
-      <c r="B99" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C99" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" s="2">
         <v>8.935341240261E12</v>
       </c>
-      <c r="B100" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C100" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" s="2">
         <v>8.935341240278E12</v>
       </c>
-      <c r="B101" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C101" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="102">
       <c r="A102" s="2">
         <v>8.935341240292E12</v>
       </c>
-      <c r="B102" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C102" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="103">
       <c r="A103" s="2">
         <v>8.935341240308E12</v>
       </c>
-      <c r="B103" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C103" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="104">
       <c r="A104" s="2">
         <v>8.935341219021E12</v>
       </c>
-      <c r="B104" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C104" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="105">
       <c r="A105" s="2">
         <v>8.935341218994E12</v>
       </c>
-      <c r="B105" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C105" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="106">
       <c r="A106" s="2">
         <v>8.935341219007E12</v>
       </c>
-      <c r="B106" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C106" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="107">
       <c r="A107" s="2">
         <v>8.935341243811E12</v>
       </c>
-      <c r="B107" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C107" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="108">
       <c r="A108" s="2">
         <v>8.935341219083E12</v>
       </c>
-      <c r="B108" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C108" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="109">
       <c r="A109" s="2">
         <v>8.935341233386E12</v>
       </c>
-      <c r="B109" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C109" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="110">
       <c r="A110" s="2">
         <v>8.848116026581E12</v>
       </c>
-      <c r="B110" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C110" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="111">
       <c r="A111" s="2">
         <v>8.935341222649E12</v>
       </c>
-      <c r="B111" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C111" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="112">
       <c r="A112" s="2">
         <v>8.935341222656E12</v>
       </c>
-      <c r="B112" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C112" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="113">
       <c r="A113" s="2">
         <v>8.935341222663E12</v>
       </c>
-      <c r="B113" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C113" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="114">
       <c r="A114" s="2">
         <v>8.93534122267E12</v>
       </c>
-      <c r="B114" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C114" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="115">
       <c r="A115" s="2">
         <v>8.935341222632E12</v>
       </c>
-      <c r="B115" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C115" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="116">
       <c r="A116" s="2">
         <v>8.935341222601E12</v>
       </c>
-      <c r="B116" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C116" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="117">
       <c r="A117" s="2">
         <v>8.935341222618E12</v>
       </c>
-      <c r="B117" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C117" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="118">
       <c r="A118" s="2">
         <v>8.935341222625E12</v>
       </c>
-      <c r="B118" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C118" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="119">
       <c r="A119" s="2">
         <v>8.935341219342E12</v>
       </c>
-      <c r="B119" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C119" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="120">
       <c r="A120" s="2">
         <v>8.93534121938E12</v>
       </c>
-      <c r="B120" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C120" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="121">
       <c r="A121" s="2">
         <v>8.935341219403E12</v>
       </c>
-      <c r="B121" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C121" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="122">
       <c r="A122" s="2">
         <v>8.935341219397E12</v>
       </c>
-      <c r="B122" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C122" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="123">
       <c r="A123" s="2">
         <v>8.935341219441E12</v>
       </c>
-      <c r="B123" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C123" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="124">
       <c r="A124" s="2">
         <v>8.93534121941E12</v>
       </c>
-      <c r="B124" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C124" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="125">
       <c r="A125" s="2">
         <v>8.935341243798E12</v>
       </c>
-      <c r="B125" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C125" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="126">
       <c r="A126" s="2">
         <v>8.935341219373E12</v>
       </c>
-      <c r="B126" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C126" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="127">
       <c r="A127" s="2">
         <v>8.935341219359E12</v>
       </c>
-      <c r="B127" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C127" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="128">
       <c r="A128" s="2">
         <v>8.935341219311E12</v>
       </c>
-      <c r="B128" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C128" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="129">
       <c r="A129" s="2">
         <v>8.935341219366E12</v>
       </c>
-      <c r="B129" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C129" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="130">
       <c r="A130" s="2">
         <v>8.935341219328E12</v>
       </c>
-      <c r="B130" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C130" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="131">
       <c r="A131" s="2">
         <v>8.935341219458E12</v>
       </c>
-      <c r="B131" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C131" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="132">
       <c r="A132" s="2">
         <v>8.935341219434E12</v>
       </c>
-      <c r="B132" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C132" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="133">
       <c r="A133" s="2">
         <v>8.935341219335E12</v>
       </c>
-      <c r="B133" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C133" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="134">
       <c r="A134" s="2">
         <v>8.935341219304E12</v>
       </c>
-      <c r="B134" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C134" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="135">
       <c r="A135" s="2">
         <v>8.935341219298E12</v>
       </c>
-      <c r="B135" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C135" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="136">
       <c r="A136" s="2">
         <v>8.935341219281E12</v>
       </c>
-      <c r="B136" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C136" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="137">
       <c r="A137" s="2">
         <v>8.935341233492E12</v>
       </c>
-      <c r="B137" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C137" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="138">
       <c r="A138" s="2">
         <v>8.935341233522E12</v>
       </c>
-      <c r="B138" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C138" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="139">
       <c r="A139" s="2">
         <v>8.935341233508E12</v>
       </c>
-      <c r="B139" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C139" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="140">
       <c r="A140" s="2">
         <v>8.935341233515E12</v>
       </c>
-      <c r="B140" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C140" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="141">
       <c r="A141" s="2">
         <v>8.935341233553E12</v>
       </c>
-      <c r="B141" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C141" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="142">
       <c r="A142" s="2">
         <v>8.935341233591E12</v>
       </c>
-      <c r="B142" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C142" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="143">
       <c r="A143" s="2">
         <v>8.935341233607E12</v>
       </c>
-      <c r="B143" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C143" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="144">
       <c r="A144" s="2">
         <v>8.935341233614E12</v>
       </c>
-      <c r="B144" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C144" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="145">
       <c r="A145" s="2">
         <v>8.848116027717E12</v>
       </c>
-      <c r="B145" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C145" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="146">
       <c r="A146" s="2">
         <v>8.935341233669E12</v>
       </c>
-      <c r="B146" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C146" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="147">
       <c r="A147" s="2">
         <v>8.848116027847E12</v>
       </c>
-      <c r="B147" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C147" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="148">
       <c r="A148" s="2">
         <v>8.93534123372E12</v>
       </c>
-      <c r="B148" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C148" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="149">
       <c r="A149" s="2">
         <v>8.935341233683E12</v>
       </c>
-      <c r="B149" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C149" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="150">
       <c r="A150" s="2">
         <v>8.93534123369E12</v>
       </c>
-      <c r="B150" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C150" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="151">
       <c r="A151" s="2">
         <v>8.935341233706E12</v>
       </c>
-      <c r="B151" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C151" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="152">
       <c r="A152" s="2">
         <v>8.848116027762E12</v>
       </c>
-      <c r="B152" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C152" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="153">
       <c r="A153" s="2">
         <v>8.935341233737E12</v>
       </c>
-      <c r="B153" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C153" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="154">
       <c r="A154" s="2">
         <v>8.848116027861E12</v>
       </c>
-      <c r="B154" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C154" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="155">
       <c r="A155" s="2">
         <v>8.848116027885E12</v>
       </c>
-      <c r="B155" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C155" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="156">
       <c r="A156" s="2">
         <v>8.935341240391E12</v>
       </c>
-      <c r="B156" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C156" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="157">
       <c r="A157" s="2">
         <v>8.935341233874E12</v>
       </c>
-      <c r="B157" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C157" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="158">
       <c r="A158" s="2">
         <v>8.935341233904E12</v>
       </c>
-      <c r="B158" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C158" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="159">
       <c r="A159" s="2">
         <v>8.935341233911E12</v>
       </c>
-      <c r="B159" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C159" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="160">
       <c r="A160" s="2">
         <v>8.935341233935E12</v>
       </c>
-      <c r="B160" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C160" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="161">
       <c r="A161" s="2">
         <v>8.935341233942E12</v>
       </c>
-      <c r="B161" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C161" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="162">
       <c r="A162" s="2">
         <v>8.935341233959E12</v>
       </c>
-      <c r="B162" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C162" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="163">
       <c r="A163" s="2">
         <v>8.935341233973E12</v>
       </c>
-      <c r="B163" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C163" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="164">
       <c r="A164" s="2">
         <v>8.935341233997E12</v>
       </c>
-      <c r="B164" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C164" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="165">
       <c r="A165" s="2">
         <v>8.935341240384E12</v>
       </c>
-      <c r="B165" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C165" t="s" s="0">
-        <v>4</v>
-      </c>
     </row>
     <row r="166">
       <c r="A166" s="2">
         <v>8.935341234E12</v>
-      </c>
-      <c r="B166" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="C166" t="s" s="0">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
